--- a/docs/downloads/05/tbl_agri_equip_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_alaotra_ambatoharanana.xlsx
@@ -436,12 +436,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -454,12 +448,6 @@
           <t>Couteau</t>
         </is>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -508,12 +496,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -526,12 +508,6 @@
           <t>Nasse</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -544,12 +520,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -562,12 +532,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -580,12 +544,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -616,12 +574,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +586,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -701,12 +647,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -719,12 +659,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -737,12 +671,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -773,12 +701,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -809,12 +731,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -827,12 +743,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -845,12 +755,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -899,12 +803,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1097,12 +995,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1151,12 +1043,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C45">
-        <v>4</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1169,12 +1055,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C46">
-        <v>3</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1186,12 +1066,6 @@
         <is>
           <t>Soubique, produits de tis</t>
         </is>
-      </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
       </c>
     </row>
     <row r="48">
